--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等140箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等141箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>806段落130表36図（実物）</t>
+          <t>843段落137表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等141箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等153箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>843段落137表36図（実物）</t>
+          <t>926段落145表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>照会票・未回答時の扱い・確定値表を作成し、発出の準備を終えた。照会そのものは未発出である。確定値表10件のうち確定は2件（訪問介護員等181人、H12の代理指標20.4％）。</t>
+          <t>照会票・未回答時の扱い・確定値表を作成し、発出の準備を終えた。照会そのものは未発出である。確定値表10件のうち確定は2件（訪問介護員等181人、H12の代理指標20.2％）。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>926段落145表36図（実物）</t>
+          <t>928段落145表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等153箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等174箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>928段落145表36図（実物）</t>
+          <t>951段落146表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等174箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等179箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>951段落146表36図（実物）</t>
+          <t>973段落148表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等179箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等195箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>973段落148表36図（実物）</t>
+          <t>1000段落151表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等195箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等198箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1000段落151表36図（実物）</t>
+          <t>1001段落151表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等198箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等245箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1001段落151表36図（実物）</t>
+          <t>1024段落152表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等245箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等250箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1024段落152表36図（実物）</t>
+          <t>1027段落153表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等250箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等259箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1027段落153表36図（実物）</t>
+          <t>1030段落153表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等259箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等270箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1030段落153表36図（実物）</t>
+          <t>1038段落153表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等270箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等290箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1038段落153表36図（実物）</t>
+          <t>1060段落156表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1060段落156表36図（実物）</t>
+          <t>1059段落156表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等290箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等292箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1059段落156表36図（実物）</t>
+          <t>1062段落156表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
